--- a/backtest_runs/20260410_193731/by_symbol/SHEZ/SHEZ.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/SHEZ/SHEZ.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>104017.65</v>
@@ -771,7 +771,7 @@
         <v>-1456.000000000008</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>102561.65</v>
@@ -860,10 +860,10 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>103043.95</v>
@@ -909,7 +909,7 @@
         <v>-5282.549999999993</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>97761.39999999999</v>
@@ -955,7 +955,7 @@
         <v>-1742.650000000006</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>96018.74999999999</v>
@@ -1185,7 +1185,7 @@
         <v>-4458.999999999992</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>91559.75</v>
@@ -1231,7 +1231,7 @@
         <v>-327.5999999999995</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>91232.14999999999</v>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>91232.14999999999</v>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>91232.14999999999</v>
@@ -1645,7 +1645,7 @@
         <v>-2679.949999999994</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>88552.20000000001</v>
